--- a/sheets/민요/검수/군밤타령.xlsx
+++ b/sheets/민요/검수/군밤타령.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="169">
   <si>
     <t xml:space="preserve">군밤타령</t>
   </si>
@@ -3781,6 +3781,14 @@
     <t xml:space="preserve">돈
 바
 람</t>
+  </si>
+  <si>
+    <t xml:space="preserve">얼
+싸</t>
+  </si>
+  <si>
+    <t xml:space="preserve">좋
+네</t>
   </si>
 </sst>
 </file>
@@ -6525,28 +6533,28 @@
   <sheetFormatPr defaultColWidth="8.0625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="1.9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="11.37"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="11.38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="5.69"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="11.37"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="11.38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="5.69"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="11.37"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="11.38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="5.69"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="11.37"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="11.38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="5.69"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="11.37"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="11.38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="5.69"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="11.37"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="11.38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="5.69"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="11.37"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="11.38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="5.69"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="11.37"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="11.38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="1" width="5.69"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="1" width="11.37"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="1" width="11.38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="1" width="5.69"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="2" customFormat="false" ht="82.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="10" t="s">
         <v>0</v>
       </c>
@@ -6568,7 +6576,7 @@
       <c r="R2" s="10"/>
       <c r="S2" s="10"/>
     </row>
-    <row r="3" customFormat="false" ht="82.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="11"/>
       <c r="C3" s="12"/>
       <c r="D3" s="11"/>
@@ -6587,7 +6595,7 @@
         <v>95</v>
       </c>
       <c r="Q3" s="12" t="s">
-        <v>88</v>
+        <v>167</v>
       </c>
       <c r="R3" s="11" t="s">
         <v>65</v>
@@ -6596,7 +6604,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="82.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="11"/>
       <c r="C4" s="13"/>
       <c r="D4" s="11"/>
@@ -6615,7 +6623,7 @@
         <v>97</v>
       </c>
       <c r="Q4" s="13" t="s">
-        <v>98</v>
+        <v>168</v>
       </c>
       <c r="R4" s="11" t="s">
         <v>68</v>
@@ -6624,7 +6632,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="82.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="11"/>
       <c r="C5" s="13"/>
       <c r="D5" s="11"/>
@@ -6650,7 +6658,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="82.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="11"/>
       <c r="C6" s="15"/>
       <c r="D6" s="16"/>
@@ -6676,7 +6684,7 @@
       </c>
       <c r="S6" s="15"/>
     </row>
-    <row r="7" customFormat="false" ht="82.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="11"/>
       <c r="C7" s="12"/>
       <c r="D7" s="11"/>
@@ -6704,7 +6712,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="82.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="11"/>
       <c r="C8" s="13"/>
       <c r="D8" s="11"/>
@@ -6732,7 +6740,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="82.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="11"/>
       <c r="C9" s="13"/>
       <c r="D9" s="11"/>
@@ -6756,7 +6764,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="82.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="11"/>
       <c r="C10" s="15"/>
       <c r="D10" s="11"/>
@@ -6782,7 +6790,7 @@
       </c>
       <c r="S10" s="15"/>
     </row>
-    <row r="11" customFormat="false" ht="82.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="11"/>
       <c r="C11" s="12"/>
       <c r="D11" s="11"/>
@@ -6810,7 +6818,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="82.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="11"/>
       <c r="C12" s="13"/>
       <c r="D12" s="11"/>
@@ -6838,7 +6846,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="82.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="11"/>
       <c r="C13" s="13"/>
       <c r="D13" s="11"/>
@@ -6866,7 +6874,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="82.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="11"/>
       <c r="C14" s="15"/>
       <c r="D14" s="11"/>
@@ -6892,7 +6900,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="82.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="11"/>
       <c r="C15" s="12"/>
       <c r="D15" s="11"/>
@@ -6916,7 +6924,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="82.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="11"/>
       <c r="C16" s="13"/>
       <c r="D16" s="11"/>
@@ -6940,7 +6948,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="82.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="11"/>
       <c r="C17" s="13"/>
       <c r="D17" s="11"/>
@@ -6964,7 +6972,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="82.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="16"/>
       <c r="C18" s="17"/>
       <c r="D18" s="16"/>

--- a/sheets/민요/검수/군밤타령.xlsx
+++ b/sheets/민요/검수/군밤타령.xlsx
@@ -44,7 +44,7 @@
       <rPr>
         <b val="true"/>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">파일</t>
@@ -63,7 +63,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">민요</t>
@@ -80,7 +80,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">군밤타령</t>
@@ -115,7 +115,7 @@
       <rPr>
         <b val="true"/>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">박자 </t>
@@ -134,7 +134,7 @@
       <rPr>
         <b val="true"/>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">행수</t>
@@ -153,7 +153,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">정간</t>
@@ -173,7 +173,7 @@
       <rPr>
         <b val="true"/>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">비고</t>
@@ -192,7 +192,7 @@
       <rPr>
         <b val="true"/>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">노란 칸</t>
@@ -216,7 +216,7 @@
       <rPr>
         <b val="true"/>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">팔레트 외 글자</t>
@@ -235,7 +235,7 @@
       <rPr>
         <b val="true"/>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">주황 칸</t>
@@ -267,7 +267,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">비고 </t>
@@ -284,7 +284,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">박자 근사</t>
@@ -301,7 +301,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">한 장에 두 곡</t>
@@ -317,7 +317,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">민요채보</t>
@@ -334,7 +334,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">군밤타령 옹헤야</t>
@@ -353,7 +353,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">손격자 </t>
@@ -370,7 +370,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">정간</t>
@@ -387,7 +387,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">굵은 선 </t>
@@ -404,7 +404,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">칸마다 → </t>
@@ -421,7 +421,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">정간마다 칸이 있음</t>
@@ -438,7 +438,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">한 장에 두 곡</t>
@@ -455,7 +455,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">상단 띠는 제목행</t>
@@ -472,7 +472,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">왼쪽 </t>
@@ -489,7 +489,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">옹헤야</t>
@@ -506,7 +506,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">자진모리</t>
@@ -523,7 +523,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">오른쪽 </t>
@@ -540,7 +540,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">군밤타령</t>
@@ -557,7 +557,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">으로 정간 아님</t>
@@ -574,7 +574,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">율명 줄 </t>
@@ -591,7 +591,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">개</t>
@@ -608,7 +608,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">오른쪽부터</t>
@@ -625,7 +625,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">줄</t>
@@ -642,7 +642,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">은 비어 있음</t>
@@ -659,7 +659,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">줄</t>
@@ -676,7 +676,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">는 정간</t>
@@ -693,7 +693,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">지운 글자와 가사 </t>
@@ -710,7 +710,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">에</t>
@@ -727,7 +727,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">정간</t>
@@ -744,7 +744,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">에 율명이 있고 그 위로 세로선 한 줄이 그어져 있음</t>
@@ -761,7 +761,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">지운 것인지 불명</t>
@@ -778,7 +778,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">보이는 대로 적음</t>
@@ -795,7 +795,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">줄</t>
@@ -812,7 +812,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">군밤타령</t>
@@ -829,7 +829,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">바람이 분다 … 돈바람 분다 </t>
@@ -846,7 +846,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">얼싸 좋네 하 좋아 군밤이요 에헤라 생율 밤이로구나</t>
@@ -863,7 +863,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">줄</t>
@@ -880,7 +880,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">정간</t>
@@ -897,7 +897,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">는 세로줄 여러 개로 지워져 비움</t>
@@ -914,7 +914,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">정간</t>
@@ -931,7 +931,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">에 </t>
@@ -948,7 +948,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">두번</t>
@@ -965,7 +965,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">메모</t>
@@ -982,7 +982,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">줄</t>
@@ -999,7 +999,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">정간</t>
@@ -1016,7 +1016,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">을 감싼 네모와 연결</t>
@@ -1033,7 +1033,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">줄</t>
@@ -1050,7 +1050,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">옹헤야</t>
@@ -1067,7 +1067,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">줄</t>
@@ -1084,7 +1084,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">메기는 소리 </t>
@@ -1101,7 +1101,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">에헤 에헤 옹해야 어절씨구 옹해야 잘도 한다 옹해야</t>
@@ -1118,7 +1118,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">줄</t>
@@ -1135,7 +1135,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">받는 소리 </t>
@@ -1152,7 +1152,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">옹헤야 옹헤야 모두 같이 옹헤야 즐거웁게 옹헤야 노래하세 옹헤야</t>
@@ -1169,7 +1169,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">女변이 없는 古 모양</t>
@@ -1186,7 +1186,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">十이 口 안으로 내려옴</t>
@@ -1203,7 +1203,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">은 南 흘림으로</t>
@@ -1220,7 +1220,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">女변이 분명한 것만 姑로 판독</t>
@@ -1237,7 +1237,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">黃</t>
@@ -1254,7 +1254,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">潢은 같은 가락에서도 氵 유무가 섞여 있어 보이는 대로 적음</t>
@@ -1271,7 +1271,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">동그라미 친 黃은 氵 없음</t>
@@ -1288,7 +1288,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">가사 칸의 </t>
@@ -1305,7 +1305,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">표시</t>
@@ -1322,7 +1322,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">옹 앞 등</t>
@@ -1339,7 +1339,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">는 기호표 위치가 아니라 생략</t>
@@ -1356,7 +1356,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">하단 </t>
@@ -1373,7 +1373,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">박</t>
@@ -1390,7 +1390,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">메모와 양식번호 </t>
@@ -1407,7 +1407,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">은 곡과 무관</t>
@@ -1432,7 +1432,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">원본처럼 오른쪽이 </t>
@@ -1449,7 +1449,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">줄</t>
@@ -1466,7 +1466,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">악보 시트도 같은 배치</t>
@@ -1483,7 +1483,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">여러 페이지는 악보 시트 아래쪽으로 이어짐</t>
@@ -1500,7 +1500,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">빈 행 </t>
@@ -1517,7 +1517,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">개</t>
@@ -1534,7 +1534,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">인쇄 시 페이지마다 새 종이</t>
@@ -1551,7 +1551,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">줄은 항상 맨 오른쪽 두 열</t>
@@ -1568,7 +1568,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">율명</t>
@@ -1585,7 +1585,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">가사</t>
@@ -1602,7 +1602,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">박자는 </t>
@@ -1619,7 +1619,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">정간</t>
@@ -1636,7 +1636,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">박자는 </t>
@@ -1653,7 +1653,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">정간마다 가사 칸 가로선을 묶음</t>
@@ -1670,7 +1670,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">율명 글자는 가사의 두 배</t>
@@ -1687,7 +1687,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">인쇄는 </t>
@@ -1704,7 +1704,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">세로</t>
@@ -1721,7 +1721,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">원본 한 페이지 </t>
@@ -1738,7 +1738,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">종이 한 장</t>
@@ -1755,7 +1755,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">정간 번호 열</t>
@@ -1772,7 +1772,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">머리 행 없음 — 제목 행 아래 </t>
@@ -1789,7 +1789,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">번째 행이 정간 </t>
@@ -1806,7 +1806,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">이므로 행을 지우거나 끼워 넣지 말고</t>
@@ -1823,7 +1823,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">제목 병합도 풀지 말 것</t>
@@ -1840,7 +1840,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">한 장이 </t>
@@ -1857,7 +1857,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">줄을 넘으면 </t>
@@ -1874,7 +1874,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">줄씩 다음 페이지</t>
@@ -1887,7 +1887,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">정간 안에서 위→아래 순서</t>
@@ -1904,7 +1904,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">칸 안 줄바꿈으로 구분 </t>
@@ -1921,7 +1921,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">앱과 같음</t>
@@ -1943,7 +1943,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">– 연음 </t>
@@ -1960,7 +1960,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">쉼 </t>
@@ -1977,7 +1977,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">점 </t>
@@ -1994,7 +1994,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">동그라미 </t>
@@ -2011,7 +2011,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">두 점 </t>
@@ -2028,7 +2028,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">정간 경계 표시 </t>
@@ -2045,7 +2045,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">／ 사선 </t>
@@ -2062,7 +2062,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">／ 는 화면 표시 전용</t>
@@ -2090,7 +2090,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">율명</t>
@@ -2107,7 +2107,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">기호표에 없는 글자 </t>
@@ -2124,7 +2124,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">포함</t>
@@ -2141,7 +2141,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">반드시 수정</t>
@@ -2154,7 +2154,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">악보 시트를 고쳐 </t>
@@ -2171,7 +2171,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">로 저장한 뒤 </t>
@@ -2188,7 +2188,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">작업</t>
@@ -2205,7 +2205,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">실행 → </t>
@@ -2222,7 +2222,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">반영</t>
@@ -2239,7 +2239,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">정보</t>
@@ -2256,7 +2256,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">정간목록 시트는 반영 안 됨</t>
@@ -2279,7 +2279,7 @@
       <rPr>
         <b val="true"/>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">율명</t>
@@ -2298,7 +2298,7 @@
       <rPr>
         <b val="true"/>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">판독</t>
@@ -2319,7 +2319,7 @@
       <rPr>
         <b val="true"/>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">율명</t>
@@ -2338,7 +2338,7 @@
       <rPr>
         <b val="true"/>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">앱</t>
@@ -2370,7 +2370,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">지운 글자</t>
@@ -2387,7 +2387,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">동그라미</t>
@@ -2404,7 +2404,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">가새표</t>
@@ -2421,7 +2421,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">비움</t>
@@ -2434,7 +2434,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">汰</t>
@@ -2451,7 +2451,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">汰</t>
@@ -2465,7 +2465,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">정간</t>
@@ -2482,7 +2482,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">위로 세로선 한 줄 그어짐</t>
@@ -2501,7 +2501,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">汰</t>
@@ -2521,7 +2521,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">汰</t>
@@ -2540,7 +2540,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">汰</t>
@@ -2557,7 +2557,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">潢</t>
@@ -2574,7 +2574,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">汰</t>
@@ -2592,7 +2592,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">潢</t>
@@ -2609,7 +2609,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">南</t>
@@ -2623,7 +2623,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">無</t>
@@ -2640,7 +2640,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">南</t>
@@ -2660,7 +2660,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">汰</t>
@@ -2677,7 +2677,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">南</t>
@@ -2695,7 +2695,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">潢</t>
@@ -2712,7 +2712,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">潢</t>
@@ -2746,7 +2746,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">汰</t>
@@ -2763,7 +2763,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">㴌</t>
@@ -2778,7 +2778,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">黃</t>
@@ -2795,7 +2795,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">潢</t>
@@ -2813,7 +2813,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">첫 黃 동그라미 침</t>
@@ -2830,7 +2830,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">氵 없음</t>
@@ -2849,7 +2849,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">南</t>
@@ -2866,7 +2866,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">無</t>
@@ -2883,7 +2883,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">南</t>
@@ -2901,7 +2901,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">南</t>
@@ -2918,7 +2918,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">姑 흘림</t>
@@ -2935,7 +2935,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">女변 없어 南</t>
@@ -2951,7 +2951,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">潢</t>
@@ -2968,7 +2968,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">黃</t>
@@ -2985,7 +2985,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">끝 黃 동그라미 침</t>
@@ -3002,7 +3002,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">氵 없음</t>
@@ -3021,7 +3021,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">姑</t>
@@ -3038,7 +3038,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">林</t>
@@ -3052,7 +3052,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">南</t>
@@ -3069,7 +3069,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">林</t>
@@ -3087,7 +3087,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">㴌</t>
@@ -3104,7 +3104,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">汰</t>
@@ -3121,7 +3121,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">潢</t>
@@ -3139,7 +3139,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">林</t>
@@ -3156,7 +3156,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">潢</t>
@@ -3174,7 +3174,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">汰</t>
@@ -3191,7 +3191,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">黃</t>
@@ -3209,7 +3209,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">黃 동그라미 침</t>
@@ -3226,7 +3226,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">氵 없음</t>
@@ -3245,7 +3245,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">潢</t>
@@ -3262,7 +3262,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">汰</t>
@@ -3279,7 +3279,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">潢</t>
@@ -3297,7 +3297,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">南</t>
@@ -3323,7 +3323,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">林</t>
@@ -3340,7 +3340,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">南</t>
@@ -3357,7 +3357,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">林</t>
@@ -3384,7 +3384,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">汰</t>
@@ -3401,7 +3401,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">黃</t>
@@ -3418,7 +3418,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">姑</t>
@@ -3435,7 +3435,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">汰</t>
@@ -3452,7 +3452,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">汰</t>
@@ -3469,7 +3469,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">潢</t>
@@ -3495,7 +3495,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">南</t>
@@ -3512,7 +3512,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">林</t>
@@ -3532,7 +3532,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">南</t>
@@ -3549,7 +3549,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">南</t>
@@ -3563,7 +3563,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">왼쪽에 </t>
@@ -3580,7 +3580,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">박</t>
@@ -3597,7 +3597,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">메모</t>
@@ -3607,7 +3607,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">潢</t>
@@ -3624,7 +3624,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">南</t>
@@ -3642,7 +3642,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">南</t>
@@ -3659,7 +3659,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">南</t>
@@ -3686,7 +3686,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">潢</t>
@@ -3703,7 +3703,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">林</t>
@@ -3798,31 +3798,31 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <sz val="11"/>
-      <name val="나눔고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="궁서체"/>
       <family val="0"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="궁서체"/>
       <family val="0"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="궁서체"/>
       <family val="0"/>
     </font>
     <font>
       <b val="true"/>
       <sz val="11"/>
-      <name val="나눔고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
@@ -3841,17 +3841,17 @@
     <font>
       <b val="true"/>
       <sz val="24"/>
-      <name val="나눔고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="24"/>
-      <name val="나눔고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
-      <name val="나눔고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
@@ -3859,6 +3859,11 @@
       <name val="궁서체"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <name val="궁서체"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -3951,7 +3956,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="32">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -4029,6 +4034,54 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="3" borderId="4" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="3" borderId="3" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="3" borderId="2" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -6533,466 +6586,466 @@
   <sheetFormatPr defaultColWidth="8.0625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="1.9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="11.38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="5.69"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="11.38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="5.69"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="11.38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="5.69"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="11.38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="5.69"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="11.38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="5.69"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="11.38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="5.69"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="11.38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="5.69"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="11.38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="1" width="5.69"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="1" width="11.38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="1" width="5.69"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="20" width="11.38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="21" width="5.69"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="20" width="11.38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="21" width="5.69"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="20" width="11.38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="21" width="5.69"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="20" width="11.38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="21" width="5.69"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="20" width="11.38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="21" width="5.69"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="20" width="11.38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="21" width="5.69"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="20" width="11.38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="21" width="5.69"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="20" width="11.38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="21" width="5.69"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="20" width="11.38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="21" width="5.69"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="2" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10"/>
-      <c r="H2" s="10"/>
-      <c r="I2" s="10"/>
-      <c r="J2" s="10"/>
-      <c r="K2" s="10"/>
-      <c r="L2" s="10"/>
-      <c r="M2" s="10"/>
-      <c r="N2" s="10"/>
-      <c r="O2" s="10"/>
-      <c r="P2" s="10"/>
-      <c r="Q2" s="10"/>
-      <c r="R2" s="10"/>
-      <c r="S2" s="10"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="22"/>
+      <c r="H2" s="22"/>
+      <c r="I2" s="22"/>
+      <c r="J2" s="22"/>
+      <c r="K2" s="22"/>
+      <c r="L2" s="22"/>
+      <c r="M2" s="22"/>
+      <c r="N2" s="22"/>
+      <c r="O2" s="22"/>
+      <c r="P2" s="22"/>
+      <c r="Q2" s="22"/>
+      <c r="R2" s="22"/>
+      <c r="S2" s="22"/>
     </row>
     <row r="3" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="11"/>
-      <c r="C3" s="12"/>
-      <c r="D3" s="11"/>
-      <c r="E3" s="12"/>
-      <c r="F3" s="11"/>
-      <c r="G3" s="12"/>
-      <c r="H3" s="11"/>
-      <c r="I3" s="12"/>
-      <c r="J3" s="11"/>
-      <c r="K3" s="12"/>
-      <c r="L3" s="11"/>
-      <c r="M3" s="12"/>
-      <c r="N3" s="11"/>
-      <c r="O3" s="12"/>
-      <c r="P3" s="11" t="s">
+      <c r="B3" s="23"/>
+      <c r="C3" s="24"/>
+      <c r="D3" s="23"/>
+      <c r="E3" s="24"/>
+      <c r="F3" s="23"/>
+      <c r="G3" s="24"/>
+      <c r="H3" s="23"/>
+      <c r="I3" s="24"/>
+      <c r="J3" s="23"/>
+      <c r="K3" s="24"/>
+      <c r="L3" s="23"/>
+      <c r="M3" s="24"/>
+      <c r="N3" s="23"/>
+      <c r="O3" s="24"/>
+      <c r="P3" s="23" t="s">
         <v>95</v>
       </c>
-      <c r="Q3" s="12" t="s">
+      <c r="Q3" s="24" t="s">
         <v>167</v>
       </c>
-      <c r="R3" s="11" t="s">
+      <c r="R3" s="23" t="s">
         <v>65</v>
       </c>
-      <c r="S3" s="12" t="s">
+      <c r="S3" s="24" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="11"/>
-      <c r="C4" s="13"/>
-      <c r="D4" s="11"/>
-      <c r="E4" s="13"/>
-      <c r="F4" s="11"/>
-      <c r="G4" s="13"/>
-      <c r="H4" s="11"/>
-      <c r="I4" s="13"/>
-      <c r="J4" s="11"/>
-      <c r="K4" s="13"/>
-      <c r="L4" s="11"/>
-      <c r="M4" s="13"/>
-      <c r="N4" s="11"/>
-      <c r="O4" s="13"/>
-      <c r="P4" s="11" t="s">
+      <c r="B4" s="23"/>
+      <c r="C4" s="25"/>
+      <c r="D4" s="23"/>
+      <c r="E4" s="25"/>
+      <c r="F4" s="23"/>
+      <c r="G4" s="25"/>
+      <c r="H4" s="23"/>
+      <c r="I4" s="25"/>
+      <c r="J4" s="23"/>
+      <c r="K4" s="25"/>
+      <c r="L4" s="23"/>
+      <c r="M4" s="25"/>
+      <c r="N4" s="23"/>
+      <c r="O4" s="25"/>
+      <c r="P4" s="23" t="s">
         <v>97</v>
       </c>
-      <c r="Q4" s="13" t="s">
+      <c r="Q4" s="25" t="s">
         <v>168</v>
       </c>
-      <c r="R4" s="11" t="s">
+      <c r="R4" s="23" t="s">
         <v>68</v>
       </c>
-      <c r="S4" s="13" t="s">
+      <c r="S4" s="25" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="11"/>
-      <c r="C5" s="13"/>
-      <c r="D5" s="11"/>
-      <c r="E5" s="13"/>
-      <c r="F5" s="11"/>
-      <c r="G5" s="13"/>
-      <c r="H5" s="11"/>
-      <c r="I5" s="13"/>
-      <c r="J5" s="11"/>
-      <c r="K5" s="13"/>
-      <c r="L5" s="11"/>
-      <c r="M5" s="13"/>
-      <c r="N5" s="11"/>
-      <c r="O5" s="13"/>
-      <c r="P5" s="14" t="s">
+      <c r="B5" s="23"/>
+      <c r="C5" s="25"/>
+      <c r="D5" s="23"/>
+      <c r="E5" s="25"/>
+      <c r="F5" s="23"/>
+      <c r="G5" s="25"/>
+      <c r="H5" s="23"/>
+      <c r="I5" s="25"/>
+      <c r="J5" s="23"/>
+      <c r="K5" s="25"/>
+      <c r="L5" s="23"/>
+      <c r="M5" s="25"/>
+      <c r="N5" s="23"/>
+      <c r="O5" s="25"/>
+      <c r="P5" s="26" t="s">
         <v>74</v>
       </c>
-      <c r="Q5" s="13"/>
-      <c r="R5" s="11" t="s">
+      <c r="Q5" s="25"/>
+      <c r="R5" s="23" t="s">
         <v>71</v>
       </c>
-      <c r="S5" s="13" t="s">
+      <c r="S5" s="25" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="11"/>
-      <c r="C6" s="15"/>
-      <c r="D6" s="16"/>
-      <c r="E6" s="17"/>
-      <c r="F6" s="11"/>
-      <c r="G6" s="15"/>
-      <c r="H6" s="11"/>
-      <c r="I6" s="15"/>
-      <c r="J6" s="11"/>
-      <c r="K6" s="15"/>
-      <c r="L6" s="11"/>
-      <c r="M6" s="15"/>
-      <c r="N6" s="11"/>
-      <c r="O6" s="15"/>
-      <c r="P6" s="11" t="s">
+      <c r="B6" s="23"/>
+      <c r="C6" s="27"/>
+      <c r="D6" s="28"/>
+      <c r="E6" s="29"/>
+      <c r="F6" s="23"/>
+      <c r="G6" s="27"/>
+      <c r="H6" s="23"/>
+      <c r="I6" s="27"/>
+      <c r="J6" s="23"/>
+      <c r="K6" s="27"/>
+      <c r="L6" s="23"/>
+      <c r="M6" s="27"/>
+      <c r="N6" s="23"/>
+      <c r="O6" s="27"/>
+      <c r="P6" s="23" t="s">
         <v>100</v>
       </c>
-      <c r="Q6" s="15" t="s">
+      <c r="Q6" s="27" t="s">
         <v>155</v>
       </c>
-      <c r="R6" s="14" t="s">
+      <c r="R6" s="26" t="s">
         <v>156</v>
       </c>
-      <c r="S6" s="15"/>
+      <c r="S6" s="27"/>
     </row>
     <row r="7" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="11"/>
-      <c r="C7" s="12"/>
-      <c r="D7" s="11"/>
-      <c r="E7" s="12"/>
-      <c r="F7" s="11"/>
-      <c r="G7" s="12"/>
-      <c r="H7" s="11"/>
-      <c r="I7" s="12"/>
-      <c r="J7" s="11"/>
-      <c r="K7" s="12"/>
-      <c r="L7" s="11"/>
-      <c r="M7" s="12"/>
-      <c r="N7" s="11"/>
-      <c r="O7" s="12"/>
-      <c r="P7" s="11" t="s">
+      <c r="B7" s="23"/>
+      <c r="C7" s="24"/>
+      <c r="D7" s="23"/>
+      <c r="E7" s="24"/>
+      <c r="F7" s="23"/>
+      <c r="G7" s="24"/>
+      <c r="H7" s="23"/>
+      <c r="I7" s="24"/>
+      <c r="J7" s="23"/>
+      <c r="K7" s="24"/>
+      <c r="L7" s="23"/>
+      <c r="M7" s="24"/>
+      <c r="N7" s="23"/>
+      <c r="O7" s="24"/>
+      <c r="P7" s="23" t="s">
         <v>103</v>
       </c>
-      <c r="Q7" s="12" t="s">
+      <c r="Q7" s="24" t="s">
         <v>157</v>
       </c>
-      <c r="R7" s="11" t="s">
+      <c r="R7" s="23" t="s">
         <v>65</v>
       </c>
-      <c r="S7" s="12" t="s">
+      <c r="S7" s="24" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="11"/>
-      <c r="C8" s="13"/>
-      <c r="D8" s="11"/>
-      <c r="E8" s="13"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="13"/>
-      <c r="H8" s="16"/>
-      <c r="I8" s="18"/>
-      <c r="J8" s="11"/>
-      <c r="K8" s="13"/>
-      <c r="L8" s="11"/>
-      <c r="M8" s="13"/>
-      <c r="N8" s="11"/>
-      <c r="O8" s="13"/>
-      <c r="P8" s="16" t="s">
+      <c r="B8" s="23"/>
+      <c r="C8" s="25"/>
+      <c r="D8" s="23"/>
+      <c r="E8" s="25"/>
+      <c r="F8" s="23"/>
+      <c r="G8" s="25"/>
+      <c r="H8" s="28"/>
+      <c r="I8" s="30"/>
+      <c r="J8" s="23"/>
+      <c r="K8" s="25"/>
+      <c r="L8" s="23"/>
+      <c r="M8" s="25"/>
+      <c r="N8" s="23"/>
+      <c r="O8" s="25"/>
+      <c r="P8" s="28" t="s">
         <v>106</v>
       </c>
-      <c r="Q8" s="18" t="s">
+      <c r="Q8" s="30" t="s">
         <v>158</v>
       </c>
-      <c r="R8" s="11" t="s">
+      <c r="R8" s="23" t="s">
         <v>68</v>
       </c>
-      <c r="S8" s="13" t="s">
+      <c r="S8" s="25" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="11"/>
-      <c r="C9" s="13"/>
-      <c r="D9" s="11"/>
-      <c r="E9" s="13"/>
-      <c r="F9" s="11"/>
-      <c r="G9" s="13"/>
-      <c r="H9" s="11"/>
-      <c r="I9" s="13"/>
-      <c r="J9" s="11"/>
-      <c r="K9" s="13"/>
-      <c r="L9" s="11"/>
-      <c r="M9" s="13"/>
-      <c r="N9" s="11"/>
-      <c r="O9" s="13"/>
-      <c r="P9" s="11"/>
-      <c r="Q9" s="13"/>
-      <c r="R9" s="11" t="s">
+      <c r="B9" s="23"/>
+      <c r="C9" s="25"/>
+      <c r="D9" s="23"/>
+      <c r="E9" s="25"/>
+      <c r="F9" s="23"/>
+      <c r="G9" s="25"/>
+      <c r="H9" s="23"/>
+      <c r="I9" s="25"/>
+      <c r="J9" s="23"/>
+      <c r="K9" s="25"/>
+      <c r="L9" s="23"/>
+      <c r="M9" s="25"/>
+      <c r="N9" s="23"/>
+      <c r="O9" s="25"/>
+      <c r="P9" s="23"/>
+      <c r="Q9" s="25"/>
+      <c r="R9" s="23" t="s">
         <v>71</v>
       </c>
-      <c r="S9" s="13" t="s">
+      <c r="S9" s="25" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="11"/>
-      <c r="C10" s="15"/>
-      <c r="D10" s="11"/>
-      <c r="E10" s="15"/>
-      <c r="F10" s="11"/>
-      <c r="G10" s="15"/>
-      <c r="H10" s="11"/>
-      <c r="I10" s="15"/>
-      <c r="J10" s="11"/>
-      <c r="K10" s="15"/>
-      <c r="L10" s="11"/>
-      <c r="M10" s="15"/>
-      <c r="N10" s="11"/>
-      <c r="O10" s="15"/>
-      <c r="P10" s="11" t="s">
+      <c r="B10" s="23"/>
+      <c r="C10" s="27"/>
+      <c r="D10" s="23"/>
+      <c r="E10" s="27"/>
+      <c r="F10" s="23"/>
+      <c r="G10" s="27"/>
+      <c r="H10" s="23"/>
+      <c r="I10" s="27"/>
+      <c r="J10" s="23"/>
+      <c r="K10" s="27"/>
+      <c r="L10" s="23"/>
+      <c r="M10" s="27"/>
+      <c r="N10" s="23"/>
+      <c r="O10" s="27"/>
+      <c r="P10" s="23" t="s">
         <v>110</v>
       </c>
-      <c r="Q10" s="15" t="s">
+      <c r="Q10" s="27" t="s">
         <v>159</v>
       </c>
-      <c r="R10" s="14" t="s">
+      <c r="R10" s="26" t="s">
         <v>156</v>
       </c>
-      <c r="S10" s="15"/>
+      <c r="S10" s="27"/>
     </row>
     <row r="11" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="11"/>
-      <c r="C11" s="12"/>
-      <c r="D11" s="11"/>
-      <c r="E11" s="12"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="12"/>
-      <c r="H11" s="11"/>
-      <c r="I11" s="12"/>
-      <c r="J11" s="11"/>
-      <c r="K11" s="12"/>
-      <c r="L11" s="11"/>
-      <c r="M11" s="12"/>
-      <c r="N11" s="11"/>
-      <c r="O11" s="12"/>
-      <c r="P11" s="11" t="s">
+      <c r="B11" s="23"/>
+      <c r="C11" s="24"/>
+      <c r="D11" s="23"/>
+      <c r="E11" s="24"/>
+      <c r="F11" s="23"/>
+      <c r="G11" s="24"/>
+      <c r="H11" s="23"/>
+      <c r="I11" s="24"/>
+      <c r="J11" s="23"/>
+      <c r="K11" s="24"/>
+      <c r="L11" s="23"/>
+      <c r="M11" s="24"/>
+      <c r="N11" s="23"/>
+      <c r="O11" s="24"/>
+      <c r="P11" s="23" t="s">
         <v>160</v>
       </c>
-      <c r="Q11" s="12" t="s">
+      <c r="Q11" s="24" t="s">
         <v>161</v>
       </c>
-      <c r="R11" s="11" t="s">
+      <c r="R11" s="23" t="s">
         <v>75</v>
       </c>
-      <c r="S11" s="12" t="s">
+      <c r="S11" s="24" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="11"/>
-      <c r="C12" s="13"/>
-      <c r="D12" s="11"/>
-      <c r="E12" s="13"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="13"/>
-      <c r="H12" s="11"/>
-      <c r="I12" s="13"/>
-      <c r="J12" s="11"/>
-      <c r="K12" s="13"/>
-      <c r="L12" s="11"/>
-      <c r="M12" s="13"/>
-      <c r="N12" s="11"/>
-      <c r="O12" s="13"/>
-      <c r="P12" s="11" t="s">
+      <c r="B12" s="23"/>
+      <c r="C12" s="25"/>
+      <c r="D12" s="23"/>
+      <c r="E12" s="25"/>
+      <c r="F12" s="23"/>
+      <c r="G12" s="25"/>
+      <c r="H12" s="23"/>
+      <c r="I12" s="25"/>
+      <c r="J12" s="23"/>
+      <c r="K12" s="25"/>
+      <c r="L12" s="23"/>
+      <c r="M12" s="25"/>
+      <c r="N12" s="23"/>
+      <c r="O12" s="25"/>
+      <c r="P12" s="23" t="s">
         <v>116</v>
       </c>
-      <c r="Q12" s="13" t="s">
+      <c r="Q12" s="25" t="s">
         <v>162</v>
       </c>
-      <c r="R12" s="11" t="s">
+      <c r="R12" s="23" t="s">
         <v>65</v>
       </c>
-      <c r="S12" s="13" t="s">
+      <c r="S12" s="25" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="11"/>
-      <c r="C13" s="13"/>
-      <c r="D13" s="11"/>
-      <c r="E13" s="13"/>
-      <c r="F13" s="11"/>
-      <c r="G13" s="13"/>
-      <c r="H13" s="11"/>
-      <c r="I13" s="13"/>
-      <c r="J13" s="11"/>
-      <c r="K13" s="13"/>
-      <c r="L13" s="11"/>
-      <c r="M13" s="13"/>
-      <c r="N13" s="11"/>
-      <c r="O13" s="13"/>
-      <c r="P13" s="11" t="s">
+      <c r="B13" s="23"/>
+      <c r="C13" s="25"/>
+      <c r="D13" s="23"/>
+      <c r="E13" s="25"/>
+      <c r="F13" s="23"/>
+      <c r="G13" s="25"/>
+      <c r="H13" s="23"/>
+      <c r="I13" s="25"/>
+      <c r="J13" s="23"/>
+      <c r="K13" s="25"/>
+      <c r="L13" s="23"/>
+      <c r="M13" s="25"/>
+      <c r="N13" s="23"/>
+      <c r="O13" s="25"/>
+      <c r="P13" s="23" t="s">
         <v>71</v>
       </c>
-      <c r="Q13" s="13" t="s">
+      <c r="Q13" s="25" t="s">
         <v>163</v>
       </c>
-      <c r="R13" s="11" t="s">
+      <c r="R13" s="23" t="s">
         <v>79</v>
       </c>
-      <c r="S13" s="13" t="s">
+      <c r="S13" s="25" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="11"/>
-      <c r="C14" s="15"/>
-      <c r="D14" s="11"/>
-      <c r="E14" s="15"/>
-      <c r="F14" s="11"/>
-      <c r="G14" s="15"/>
-      <c r="H14" s="11"/>
-      <c r="I14" s="15"/>
-      <c r="J14" s="16"/>
-      <c r="K14" s="17"/>
-      <c r="L14" s="11"/>
-      <c r="M14" s="15"/>
-      <c r="N14" s="11"/>
-      <c r="O14" s="15"/>
-      <c r="P14" s="14" t="s">
+      <c r="B14" s="23"/>
+      <c r="C14" s="27"/>
+      <c r="D14" s="23"/>
+      <c r="E14" s="27"/>
+      <c r="F14" s="23"/>
+      <c r="G14" s="27"/>
+      <c r="H14" s="23"/>
+      <c r="I14" s="27"/>
+      <c r="J14" s="28"/>
+      <c r="K14" s="29"/>
+      <c r="L14" s="23"/>
+      <c r="M14" s="27"/>
+      <c r="N14" s="23"/>
+      <c r="O14" s="27"/>
+      <c r="P14" s="26" t="s">
         <v>74</v>
       </c>
-      <c r="Q14" s="15"/>
-      <c r="R14" s="16" t="s">
+      <c r="Q14" s="27"/>
+      <c r="R14" s="28" t="s">
         <v>81</v>
       </c>
-      <c r="S14" s="17" t="s">
+      <c r="S14" s="29" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="11"/>
-      <c r="C15" s="12"/>
-      <c r="D15" s="11"/>
-      <c r="E15" s="12"/>
-      <c r="F15" s="11"/>
-      <c r="G15" s="12"/>
-      <c r="H15" s="11"/>
-      <c r="I15" s="12"/>
-      <c r="J15" s="16"/>
-      <c r="K15" s="19"/>
-      <c r="L15" s="11"/>
-      <c r="M15" s="12"/>
-      <c r="N15" s="11"/>
-      <c r="O15" s="12"/>
-      <c r="P15" s="11"/>
-      <c r="Q15" s="12"/>
-      <c r="R15" s="16" t="s">
+      <c r="B15" s="23"/>
+      <c r="C15" s="24"/>
+      <c r="D15" s="23"/>
+      <c r="E15" s="24"/>
+      <c r="F15" s="23"/>
+      <c r="G15" s="24"/>
+      <c r="H15" s="23"/>
+      <c r="I15" s="24"/>
+      <c r="J15" s="28"/>
+      <c r="K15" s="31"/>
+      <c r="L15" s="23"/>
+      <c r="M15" s="24"/>
+      <c r="N15" s="23"/>
+      <c r="O15" s="24"/>
+      <c r="P15" s="23"/>
+      <c r="Q15" s="24"/>
+      <c r="R15" s="28" t="s">
         <v>85</v>
       </c>
-      <c r="S15" s="19" t="s">
+      <c r="S15" s="31" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="11"/>
-      <c r="C16" s="13"/>
-      <c r="D16" s="11"/>
-      <c r="E16" s="13"/>
-      <c r="F16" s="11"/>
-      <c r="G16" s="13"/>
-      <c r="H16" s="11"/>
-      <c r="I16" s="13"/>
-      <c r="J16" s="11"/>
-      <c r="K16" s="13"/>
-      <c r="L16" s="11"/>
-      <c r="M16" s="13"/>
-      <c r="N16" s="11"/>
-      <c r="O16" s="13"/>
-      <c r="P16" s="11"/>
-      <c r="Q16" s="13"/>
-      <c r="R16" s="11" t="s">
+      <c r="B16" s="23"/>
+      <c r="C16" s="25"/>
+      <c r="D16" s="23"/>
+      <c r="E16" s="25"/>
+      <c r="F16" s="23"/>
+      <c r="G16" s="25"/>
+      <c r="H16" s="23"/>
+      <c r="I16" s="25"/>
+      <c r="J16" s="23"/>
+      <c r="K16" s="25"/>
+      <c r="L16" s="23"/>
+      <c r="M16" s="25"/>
+      <c r="N16" s="23"/>
+      <c r="O16" s="25"/>
+      <c r="P16" s="23"/>
+      <c r="Q16" s="25"/>
+      <c r="R16" s="23" t="s">
         <v>71</v>
       </c>
-      <c r="S16" s="13" t="s">
+      <c r="S16" s="25" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="11"/>
-      <c r="C17" s="13"/>
-      <c r="D17" s="11"/>
-      <c r="E17" s="13"/>
-      <c r="F17" s="11"/>
-      <c r="G17" s="13"/>
-      <c r="H17" s="11"/>
-      <c r="I17" s="13"/>
-      <c r="J17" s="11"/>
-      <c r="K17" s="13"/>
-      <c r="L17" s="11"/>
-      <c r="M17" s="13"/>
-      <c r="N17" s="11"/>
-      <c r="O17" s="13"/>
-      <c r="P17" s="11"/>
-      <c r="Q17" s="13"/>
-      <c r="R17" s="11" t="s">
+      <c r="B17" s="23"/>
+      <c r="C17" s="25"/>
+      <c r="D17" s="23"/>
+      <c r="E17" s="25"/>
+      <c r="F17" s="23"/>
+      <c r="G17" s="25"/>
+      <c r="H17" s="23"/>
+      <c r="I17" s="25"/>
+      <c r="J17" s="23"/>
+      <c r="K17" s="25"/>
+      <c r="L17" s="23"/>
+      <c r="M17" s="25"/>
+      <c r="N17" s="23"/>
+      <c r="O17" s="25"/>
+      <c r="P17" s="23"/>
+      <c r="Q17" s="25"/>
+      <c r="R17" s="23" t="s">
         <v>85</v>
       </c>
-      <c r="S17" s="13" t="s">
+      <c r="S17" s="25" t="s">
         <v>166</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="16"/>
-      <c r="C18" s="17"/>
-      <c r="D18" s="16"/>
-      <c r="E18" s="17"/>
-      <c r="F18" s="11"/>
-      <c r="G18" s="15"/>
-      <c r="H18" s="11"/>
-      <c r="I18" s="15"/>
-      <c r="J18" s="16"/>
-      <c r="K18" s="17"/>
-      <c r="L18" s="11"/>
-      <c r="M18" s="15"/>
-      <c r="N18" s="11"/>
-      <c r="O18" s="15"/>
-      <c r="P18" s="11"/>
-      <c r="Q18" s="15"/>
-      <c r="R18" s="16" t="s">
+      <c r="B18" s="28"/>
+      <c r="C18" s="29"/>
+      <c r="D18" s="28"/>
+      <c r="E18" s="29"/>
+      <c r="F18" s="23"/>
+      <c r="G18" s="27"/>
+      <c r="H18" s="23"/>
+      <c r="I18" s="27"/>
+      <c r="J18" s="28"/>
+      <c r="K18" s="29"/>
+      <c r="L18" s="23"/>
+      <c r="M18" s="27"/>
+      <c r="N18" s="23"/>
+      <c r="O18" s="27"/>
+      <c r="P18" s="23"/>
+      <c r="Q18" s="27"/>
+      <c r="R18" s="28" t="s">
         <v>91</v>
       </c>
-      <c r="S18" s="17" t="s">
+      <c r="S18" s="29" t="s">
         <v>154</v>
       </c>
     </row>

--- a/sheets/민요/검수/군밤타령.xlsx
+++ b/sheets/민요/검수/군밤타령.xlsx
@@ -3880,10 +3880,7 @@
       </patternFill>
     </fill>
     <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
+      <patternFill patternType="none"/>
     </fill>
   </fills>
   <borders count="5">

--- a/sheets/민요/검수/군밤타령.xlsx
+++ b/sheets/민요/검수/군밤타령.xlsx
@@ -30,70 +30,10 @@
     <t xml:space="preserve">군밤타령</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">CSV </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">파일</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">sheets/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">민요</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/csv/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">군밤타령</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.csv</t>
-    </r>
+    <t xml:space="preserve">CSV 파일</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sheets/민요/csv/군밤타령.csv</t>
   </si>
   <si>
     <t xml:space="preserve">부제</t>
@@ -111,53 +51,10 @@
     <t xml:space="preserve">쪽</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">박자 </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/ </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">행수</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">4/4 / 16</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">정간</t>
-    </r>
+    <t xml:space="preserve">박자 / 행수</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4/4 / 16정간</t>
   </si>
   <si>
     <t xml:space="preserve">페이지</t>
@@ -169,87 +66,13 @@
     <t xml:space="preserve">정간 수</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">비고</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">노란 칸</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
+    <t xml:space="preserve">비고(노란 칸)</t>
   </si>
   <si>
     <t xml:space="preserve">11</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">팔레트 외 글자</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">주황 칸</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
+    <t xml:space="preserve">팔레트 외 글자(주황 칸)</t>
   </si>
   <si>
     <t xml:space="preserve">0</t>
@@ -264,48 +87,7 @@
     <t xml:space="preserve">확인 필요</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">비고 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">17%, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">박자 근사</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">한 장에 두 곡</t>
-    </r>
+    <t xml:space="preserve">비고 17%, 박자 근사, 한 장에 두 곡</t>
   </si>
   <si>
     <t xml:space="preserve">원본 이미지</t>
@@ -314,1113 +96,10 @@
     <t xml:space="preserve">판독 메모</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">민요채보</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">-2/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">군밤타령 옹헤야</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.png</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">손격자 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">16</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">정간</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">굵은 선 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">4</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">칸마다 → </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">4/4·16), </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">정간마다 칸이 있음</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">한 장에 두 곡</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">상단 띠는 제목행</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">왼쪽 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">"</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">옹헤야</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">자진모리</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)" / </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">오른쪽 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">"</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">군밤타령</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">" / "C#→C key")</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">으로 정간 아님</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">율명 줄 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">10</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">개</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">오른쪽부터</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">): </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">줄</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1·3·4·10</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">은 비어 있음</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">줄</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">는 정간</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">지운 글자와 가사 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">'</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">에</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">', </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">정간</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">8~16</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">에 율명이 있고 그 위로 세로선 한 줄이 그어져 있음</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">지운 것인지 불명</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">보이는 대로 적음</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">). </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">줄</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">5·6 = </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">군밤타령</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">바람이 분다 … 돈바람 분다 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/ </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">얼싸 좋네 하 좋아 군밤이요 에헤라 생율 밤이로구나</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">). </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">줄</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">7 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">정간</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1~4</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">는 세로줄 여러 개로 지워져 비움</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">정간</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">5</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">에 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">'</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">두번</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">' </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">메모</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">줄</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">8 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">정간</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">5~16</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">을 감싼 네모와 연결</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">). </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">줄</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">8·9 = </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">옹헤야</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">줄</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">9 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">메기는 소리 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">'</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">에헤 에헤 옹해야 어절씨구 옹해야 잘도 한다 옹해야</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">', </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">줄</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">8 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">받는 소리 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">'</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">옹헤야 옹헤야 모두 같이 옹헤야 즐거웁게 옹헤야 노래하세 옹헤야</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">'). </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">女변이 없는 古 모양</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">十이 口 안으로 내려옴</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">은 南 흘림으로</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">女변이 분명한 것만 姑로 판독</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">黃</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">潢은 같은 가락에서도 氵 유무가 섞여 있어 보이는 대로 적음</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">동그라미 친 黃은 氵 없음</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">). </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">가사 칸의 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">&lt; </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">표시</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">옹 앞 등</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">는 기호표 위치가 아니라 생략</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">하단 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">'4</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">박</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">' </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">메모와 양식번호 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">"- 196 -"</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">은 곡과 무관</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.</t>
-    </r>
+    <t xml:space="preserve">민요채보-2/군밤타령 옹헤야.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">손격자 16정간(굵은 선 4칸마다 → 4/4·16), 정간마다 칸이 있음. 한 장에 두 곡: 상단 띠는 제목행(왼쪽 "옹헤야(자진모리)" / 오른쪽 "군밤타령" / "C#→C key")으로 정간 아님. 율명 줄 10개(오른쪽부터): 줄1·3·4·10은 비어 있음. 줄2는 정간1 지운 글자와 가사 '에', 정간8~16에 율명이 있고 그 위로 세로선 한 줄이 그어져 있음(지운 것인지 불명, 보이는 대로 적음). 줄5·6 = 군밤타령(바람이 분다 … 돈바람 분다 / 얼싸 좋네 하 좋아 군밤이요 에헤라 생율 밤이로구나). 줄7 정간1~4는 세로줄 여러 개로 지워져 비움, 정간5에 '두번' 메모(줄8 정간5~16을 감싼 네모와 연결). 줄8·9 = 옹헤야(줄9 메기는 소리 '에헤 에헤 옹해야 어절씨구 옹해야 잘도 한다 옹해야', 줄8 받는 소리 '옹헤야 옹헤야 모두 같이 옹헤야 즐거웁게 옹헤야 노래하세 옹헤야'). 女변이 없는 古 모양(十이 口 안으로 내려옴)은 南 흘림으로, 女변이 분명한 것만 姑로 판독. 黃/潢은 같은 가락에서도 氵 유무가 섞여 있어 보이는 대로 적음(동그라미 친 黃은 氵 없음). 가사 칸의 &lt; 표시(옹 앞 등)는 기호표 위치가 아니라 생략. 하단 '4박' 메모와 양식번호 "- 196 -"은 곡과 무관.</t>
   </si>
   <si>
     <t xml:space="preserve">범례</t>
@@ -1429,653 +108,19 @@
     <t xml:space="preserve">줄 순서</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">원본처럼 오른쪽이 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">줄</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">악보 시트도 같은 배치</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">여러 페이지는 악보 시트 아래쪽으로 이어짐</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">빈 행 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">개</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">인쇄 시 페이지마다 새 종이</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">). 1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">줄은 항상 맨 오른쪽 두 열</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">율명</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">가사</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">). 3/4 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">박자는 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">정간</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, 4/4 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">박자는 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">4</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">정간마다 가사 칸 가로선을 묶음</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">율명 글자는 가사의 두 배</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">인쇄는 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">A4 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">세로</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">원본 한 페이지 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">= </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">종이 한 장</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">정간 번호 열</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">머리 행 없음 — 제목 행 아래 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">n</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">번째 행이 정간 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">n</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">이므로 행을 지우거나 끼워 넣지 말고</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">제목 병합도 풀지 말 것</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">한 장이 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">10</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">줄을 넘으면 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">10</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">줄씩 다음 페이지</t>
-    </r>
+    <t xml:space="preserve">원본처럼 오른쪽이 1줄. 악보 시트도 같은 배치. 여러 페이지는 악보 시트 아래쪽으로 이어짐(빈 행 1개, 인쇄 시 페이지마다 새 종이). 1줄은 항상 맨 오른쪽 두 열(율명, 가사). 3/4 박자는 3정간, 4/4 박자는 4정간마다 가사 칸 가로선을 묶음. 율명 글자는 가사의 두 배. 인쇄는 A4 세로, 원본 한 페이지 = 종이 한 장. 정간 번호 열·머리 행 없음 — 제목 행 아래 n번째 행이 정간 n이므로 행을 지우거나 끼워 넣지 말고, 제목 병합도 풀지 말 것. 한 장이 10줄을 넘으면 10줄씩 다음 페이지</t>
   </si>
   <si>
     <t xml:space="preserve">율명 칸</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">정간 안에서 위→아래 순서</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">칸 안 줄바꿈으로 구분 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">앱과 같음</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
+    <t xml:space="preserve">정간 안에서 위→아래 순서, 칸 안 줄바꿈으로 구분 (앱과 같음)</t>
   </si>
   <si>
     <t xml:space="preserve">기호</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">– 연음 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">· △ </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">쉼 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">· </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">점 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">· ○ </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">동그라미 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">· ⁚ </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">두 점 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">· ‹ </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">정간 경계 표시 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">· </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">／ 사선 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(· ○ ⁚ ‹ </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">／ 는 화면 표시 전용</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
+    <t xml:space="preserve">– 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
   </si>
   <si>
     <t xml:space="preserve">노란 칸</t>
@@ -2087,180 +132,13 @@
     <t xml:space="preserve">주황 칸</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">율명</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">기호표에 없는 글자 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(? </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">포함</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">) — </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">반드시 수정</t>
-    </r>
+    <t xml:space="preserve">율명·기호표에 없는 글자 (? 포함) — 반드시 수정</t>
   </si>
   <si>
     <t xml:space="preserve">수정 방법</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">악보 시트를 고쳐 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.xlsx </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">로 저장한 뒤 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">작업</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/xlsx_to_csv.py </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">실행 → </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">csv </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">반영</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">정보</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">정간목록 시트는 반영 안 됨</t>
-    </r>
+    <t xml:space="preserve">악보 시트를 고쳐 .xlsx 로 저장한 뒤 _작업/xlsx_to_csv.py 실행 → csv 반영. 정보·정간목록 시트는 반영 안 됨</t>
   </si>
   <si>
     <t xml:space="preserve">줄</t>
@@ -2275,84 +153,10 @@
     <t xml:space="preserve">박</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">율명</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">판독</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">율명</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">앱</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
+    <t xml:space="preserve">율명(판독)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">율명(앱)</t>
   </si>
   <si>
     <t xml:space="preserve">가사</t>
@@ -2367,165 +171,27 @@
     <t xml:space="preserve">에</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">지운 글자</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">동그라미</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">가새표</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">), </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">비움</t>
-    </r>
+    <t xml:space="preserve">지운 글자(동그라미+가새표), 비움</t>
   </si>
   <si>
     <t xml:space="preserve">△</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">汰</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">|</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">汰</t>
-    </r>
+    <t xml:space="preserve">汰|汰</t>
   </si>
   <si>
     <t xml:space="preserve">汰
 汰</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">정간</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">8~16 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">위로 세로선 한 줄 그어짐</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">–|</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">汰</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">–
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">汰</t>
-    </r>
+    <t xml:space="preserve">정간8~16 위로 세로선 한 줄 그어짐</t>
+  </si>
+  <si>
+    <t xml:space="preserve">–|汰</t>
+  </si>
+  <si>
+    <t xml:space="preserve">–
+汰</t>
   </si>
   <si>
     <t xml:space="preserve">–</t>
@@ -2537,48 +203,7 @@
     <t xml:space="preserve">汰</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">汰</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">|</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">潢</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">|</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">汰</t>
-    </r>
+    <t xml:space="preserve">汰|潢|汰</t>
   </si>
   <si>
     <t xml:space="preserve">汰
@@ -2589,62 +214,14 @@
     <t xml:space="preserve">셋째 汰는 아래 경계에 걸침</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">潢</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">|</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">南</t>
-    </r>
+    <t xml:space="preserve">潢|南</t>
   </si>
   <si>
     <t xml:space="preserve">潢
 南</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">無</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">|</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">南</t>
-    </r>
+    <t xml:space="preserve">無|南</t>
   </si>
   <si>
     <t xml:space="preserve">無
@@ -2657,31 +234,7 @@
     <t xml:space="preserve">바</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">汰</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">|–|</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">南</t>
-    </r>
+    <t xml:space="preserve">汰|–|南</t>
   </si>
   <si>
     <t xml:space="preserve">汰
@@ -2692,31 +245,7 @@
     <t xml:space="preserve">람</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">潢</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">|–|</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">潢</t>
-    </r>
+    <t xml:space="preserve">潢|–|潢</t>
   </si>
   <si>
     <t xml:space="preserve">潢
@@ -2743,31 +272,7 @@
     <t xml:space="preserve">평</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">汰</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">|–|</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">㴌</t>
-    </r>
+    <t xml:space="preserve">汰|–|㴌</t>
   </si>
   <si>
     <t xml:space="preserve">汰
@@ -2775,31 +280,7 @@
 㴌</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">黃</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">|–|</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">潢</t>
-    </r>
+    <t xml:space="preserve">黃|–|潢</t>
   </si>
   <si>
     <t xml:space="preserve">黃
@@ -2810,84 +291,10 @@
     <t xml:space="preserve">다에</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">첫 黃 동그라미 침</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">氵 없음</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">南</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">|</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">無</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">|</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">南</t>
-    </r>
+    <t xml:space="preserve">첫 黃 동그라미 침(氵 없음)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">南|無|南</t>
   </si>
   <si>
     <t xml:space="preserve">南
@@ -2898,48 +305,7 @@
     <t xml:space="preserve">어</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">南</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">姑 흘림</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">女변 없어 南</t>
-    </r>
+    <t xml:space="preserve">南/姑 흘림, 女변 없어 南</t>
   </si>
   <si>
     <t xml:space="preserve">얼싸</t>
@@ -2948,31 +314,7 @@
     <t xml:space="preserve">돈바람</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">潢</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">|</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">黃</t>
-    </r>
+    <t xml:space="preserve">潢|黃</t>
   </si>
   <si>
     <t xml:space="preserve">潢
@@ -2982,98 +324,17 @@
     <t xml:space="preserve">분다</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">끝 黃 동그라미 침</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">氵 없음</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">姑</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">|</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">林</t>
-    </r>
+    <t xml:space="preserve">끝 黃 동그라미 침(氵 없음)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">姑|林</t>
   </si>
   <si>
     <t xml:space="preserve">姑
 林</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">南</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">|–|</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">林</t>
-    </r>
+    <t xml:space="preserve">南|–|林</t>
   </si>
   <si>
     <t xml:space="preserve">南
@@ -3084,48 +345,7 @@
     <t xml:space="preserve">좋네</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">㴌</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">|</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">汰</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">|</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">潢</t>
-    </r>
+    <t xml:space="preserve">㴌|汰|潢</t>
   </si>
   <si>
     <t xml:space="preserve">㴌
@@ -3136,31 +356,7 @@
     <t xml:space="preserve">하좋아</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">林</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">|–|</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">潢</t>
-    </r>
+    <t xml:space="preserve">林|–|潢</t>
   </si>
   <si>
     <t xml:space="preserve">林
@@ -3171,31 +367,7 @@
     <t xml:space="preserve">군밤</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">汰</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">|–|</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">黃</t>
-    </r>
+    <t xml:space="preserve">汰|–|黃</t>
   </si>
   <si>
     <t xml:space="preserve">汰
@@ -3206,84 +378,10 @@
     <t xml:space="preserve">이요</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">黃 동그라미 침</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">氵 없음</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">潢</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">|</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">汰</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">|</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">潢</t>
-    </r>
+    <t xml:space="preserve">黃 동그라미 침(氵 없음)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">潢|汰|潢</t>
   </si>
   <si>
     <t xml:space="preserve">潢
@@ -3294,23 +392,7 @@
     <t xml:space="preserve">에헤라</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">南</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">|–</t>
-    </r>
+    <t xml:space="preserve">南|–</t>
   </si>
   <si>
     <t xml:space="preserve">南
@@ -3320,48 +402,7 @@
     <t xml:space="preserve">생율</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">林</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">|</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">南</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">|</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">林</t>
-    </r>
+    <t xml:space="preserve">林|南|林</t>
   </si>
   <si>
     <t xml:space="preserve">林
@@ -3381,31 +422,7 @@
     <t xml:space="preserve">옹</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">汰</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">|</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">黃</t>
-    </r>
+    <t xml:space="preserve">汰|黃</t>
   </si>
   <si>
     <t xml:space="preserve">汰
@@ -3415,31 +432,7 @@
     <t xml:space="preserve">헤야</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">姑</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">|</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">汰</t>
-    </r>
+    <t xml:space="preserve">姑|汰</t>
   </si>
   <si>
     <t xml:space="preserve">姑
@@ -3449,31 +442,7 @@
     <t xml:space="preserve">모두</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">汰</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">|</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">潢</t>
-    </r>
+    <t xml:space="preserve">汰|潢</t>
   </si>
   <si>
     <t xml:space="preserve">汰
@@ -3492,31 +461,7 @@
     <t xml:space="preserve">노래</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">南</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">|</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">林</t>
-    </r>
+    <t xml:space="preserve">南|林</t>
   </si>
   <si>
     <t xml:space="preserve">南
@@ -3529,106 +474,17 @@
     <t xml:space="preserve">姑</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">南</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">|</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">南</t>
-    </r>
+    <t xml:space="preserve">南|南</t>
   </si>
   <si>
     <t xml:space="preserve">南
 南</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">왼쪽에 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">"4</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">박</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">" </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">메모</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">潢</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">|–|</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">南</t>
-    </r>
+    <t xml:space="preserve">왼쪽에 "4박" 메모</t>
+  </si>
+  <si>
+    <t xml:space="preserve">潢|–|南</t>
   </si>
   <si>
     <t xml:space="preserve">潢
@@ -3639,31 +495,7 @@
     <t xml:space="preserve">에헤</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">南</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">|–|</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">南</t>
-    </r>
+    <t xml:space="preserve">南|–|南</t>
   </si>
   <si>
     <t xml:space="preserve">南
@@ -3683,31 +515,7 @@
     <t xml:space="preserve">잘도</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">潢</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">|–|</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">林</t>
-    </r>
+    <t xml:space="preserve">潢|–|林</t>
   </si>
   <si>
     <t xml:space="preserve">潢
@@ -6577,7 +3385,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+    <pageSetUpPr fitToPage="0"/>
   </sheetPr>
   <dimension ref="B1:S18"/>
   <sheetFormatPr defaultColWidth="8.0625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
@@ -6603,8 +3411,8 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="21" width="5.69"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="2" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="6.0" customHeight="true"/>
+    <row r="2" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="81.63" customHeight="true">
       <c r="B2" s="22" t="s">
         <v>0</v>
       </c>
@@ -6626,7 +3434,7 @@
       <c r="R2" s="22"/>
       <c r="S2" s="22"/>
     </row>
-    <row r="3" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="91.25" customHeight="true">
       <c r="B3" s="23"/>
       <c r="C3" s="24"/>
       <c r="D3" s="23"/>
@@ -6654,7 +3462,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="91.25" customHeight="true">
       <c r="B4" s="23"/>
       <c r="C4" s="25"/>
       <c r="D4" s="23"/>
@@ -6682,7 +3490,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="91.25" customHeight="true">
       <c r="B5" s="23"/>
       <c r="C5" s="25"/>
       <c r="D5" s="23"/>
@@ -6708,7 +3516,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="91.25" customHeight="true">
       <c r="B6" s="23"/>
       <c r="C6" s="27"/>
       <c r="D6" s="28"/>
@@ -6734,7 +3542,7 @@
       </c>
       <c r="S6" s="27"/>
     </row>
-    <row r="7" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="91.25" customHeight="true">
       <c r="B7" s="23"/>
       <c r="C7" s="24"/>
       <c r="D7" s="23"/>
@@ -6762,7 +3570,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="91.25" customHeight="true">
       <c r="B8" s="23"/>
       <c r="C8" s="25"/>
       <c r="D8" s="23"/>
@@ -6790,7 +3598,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="91.25" customHeight="true">
       <c r="B9" s="23"/>
       <c r="C9" s="25"/>
       <c r="D9" s="23"/>
@@ -6814,7 +3622,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="91.25" customHeight="true">
       <c r="B10" s="23"/>
       <c r="C10" s="27"/>
       <c r="D10" s="23"/>
@@ -6840,7 +3648,7 @@
       </c>
       <c r="S10" s="27"/>
     </row>
-    <row r="11" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="91.25" customHeight="true">
       <c r="B11" s="23"/>
       <c r="C11" s="24"/>
       <c r="D11" s="23"/>
@@ -6868,7 +3676,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="91.25" customHeight="true">
       <c r="B12" s="23"/>
       <c r="C12" s="25"/>
       <c r="D12" s="23"/>
@@ -6896,7 +3704,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="91.25" customHeight="true">
       <c r="B13" s="23"/>
       <c r="C13" s="25"/>
       <c r="D13" s="23"/>
@@ -6924,7 +3732,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="91.25" customHeight="true">
       <c r="B14" s="23"/>
       <c r="C14" s="27"/>
       <c r="D14" s="23"/>
@@ -6950,7 +3758,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="91.25" customHeight="true">
       <c r="B15" s="23"/>
       <c r="C15" s="24"/>
       <c r="D15" s="23"/>
@@ -6974,7 +3782,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="91.25" customHeight="true">
       <c r="B16" s="23"/>
       <c r="C16" s="25"/>
       <c r="D16" s="23"/>
@@ -6998,7 +3806,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="91.25" customHeight="true">
       <c r="B17" s="23"/>
       <c r="C17" s="25"/>
       <c r="D17" s="23"/>
@@ -7022,7 +3830,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="91.25" customHeight="true">
       <c r="B18" s="28"/>
       <c r="C18" s="29"/>
       <c r="D18" s="28"/>
@@ -7052,7 +3860,7 @@
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="true" verticalCentered="false"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="67" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="49"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>

--- a/sheets/민요/검수/군밤타령.xlsx
+++ b/sheets/민요/검수/군밤타령.xlsx
@@ -3391,23 +3391,23 @@
   <sheetFormatPr defaultColWidth="8.0625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="1.9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="20" width="11.38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="20" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="21" width="5.69"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="20" width="11.38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="20" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="21" width="5.69"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="20" width="11.38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="20" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="21" width="5.69"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="20" width="11.38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="20" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="21" width="5.69"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="20" width="11.38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="20" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="21" width="5.69"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="20" width="11.38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="20" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="21" width="5.69"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="20" width="11.38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="20" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="21" width="5.69"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="20" width="11.38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="20" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="21" width="5.69"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="20" width="11.38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="20" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="21" width="5.69"/>
   </cols>
   <sheetData>
